--- a/jogos_2024-11-26.xlsx
+++ b/jogos_2024-11-26.xlsx
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.37</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '88']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['15', '43', '59', '70', '85', '89']</t>
+          <t>['21', '68', '71']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>2.29</v>
+        <v>4.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45622.61458333334</v>
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O10" t="n">
-        <v>9</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['24', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['21', '68', '71']</t>
+          <t>['15', '43', '59', '70', '85', '89']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>4.5</v>
+        <v>2.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45622.61458333334</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,34 +1830,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
         <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
@@ -1869,16 +1869,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
         <v>1.57</v>
@@ -1888,25 +1888,25 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['9', '65', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2.35</v>
       </c>
-      <c r="AH11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.88</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45622.66666666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Real Kings</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
         <v>3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA13" t="n">
         <v>4.75</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="AB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['3', '85']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['72', '74', '86']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.57</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X13" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AI13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.35</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['9', '65', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45622.66666666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Kings</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.2</v>
       </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
         <v>2.35</v>
       </c>
-      <c r="T14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AH14" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['3', '85']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['72', '74', '86']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AI14" t="n">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45622.66666666666</v>
@@ -2310,29 +2310,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Rampla Juniors</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Liverpool FC Montevideo</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI15" t="n">
         <v>2.25</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['57', '61', '76', '82']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45622.6875</v>
@@ -2439,29 +2439,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rampla Juniors</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liverpool FC Montevideo</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.15</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['57', '61', '76', '82']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>1.57</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45622.6875</v>
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
         <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Z17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AD17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['11', '83']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI17" t="n">
         <v>3</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45622.69791666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,34 +2991,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
         <v>1.07</v>
@@ -3027,19 +3027,19 @@
         <v>1.4</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
         <v>1.91</v>
@@ -3054,20 +3054,20 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '53']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45622.69791666666</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.65</v>
+        <v>2.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '72']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['26', '90']</t>
+          <t>['50', '66']</t>
         </is>
       </c>
       <c r="AG21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.53</v>
       </c>
-      <c r="AH21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45622.69791666666</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.1</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.63</v>
-      </c>
       <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.33</v>
       </c>
-      <c r="S22" t="n">
+      <c r="X22" t="n">
         <v>3.25</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4</v>
-      </c>
       <c r="Y22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1.78</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI22" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['27', '52']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45622.69791666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,23 +3352,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="P23" t="n">
         <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['10', '26', '58']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.33</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['7', '72']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['50', '66']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45622.69791666666</v>
@@ -3481,48 +3481,48 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>5.25</v>
+        <v>2.37</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
         <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
         <v>1.44</v>
@@ -3540,50 +3540,50 @@
         <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['11', '18']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['26', '90']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45622.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>1.73</v>
       </c>
       <c r="O25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA25" t="n">
         <v>3</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
         <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['37', '81']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45622.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="M26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O26" t="n">
         <v>3.75</v>
       </c>
-      <c r="N26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O26" t="n">
-        <v>5.5</v>
-      </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
         <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3828,20 +3828,20 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['11', '83']</t>
+          <t>['27', '52']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AI26" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45622.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.25</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.25</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
         <v>1.07</v>
@@ -3930,19 +3930,19 @@
         <v>1.4</v>
       </c>
       <c r="X27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
         <v>1.91</v>
@@ -3957,20 +3957,20 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['37', '53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45622.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -4152,22 +4152,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
         <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
         <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
         <v>1.4</v>
@@ -4185,50 +4185,50 @@
         <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45622.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,65 +4281,65 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y30" t="n">
         <v>2.05</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.77</v>
-      </c>
       <c r="Z30" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['10', '26', '58']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45622.69791666666</v>
@@ -4384,16 +4384,16 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
         <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P31" t="n">
         <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['47', '80']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.32</v>
       </c>
-      <c r="X31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45622.69791666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,16 +4513,16 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -4531,7 +4531,7 @@
         <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
         <v>5.25</v>
       </c>
       <c r="O32" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
         <v>5.5</v>
       </c>
       <c r="R32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.33</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="X32" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.43</v>
+        <v>3.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['2', '17', '51', '72', '80', '82']</t>
+          <t>['11', '18']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45622.69791666666</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="M33" t="n">
         <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="O33" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
         <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X33" t="n">
         <v>3.25</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['37', '81']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.38</v>
       </c>
-      <c r="X33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['47', '80']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45622.69791666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="O34" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="R34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U34" t="n">
         <v>1.44</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.75</v>
+        <v>2.43</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
         <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['2', '17', '51', '72', '80', '82']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45622.69791666666</v>
@@ -4900,16 +4900,16 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -4926,65 +4926,65 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="M35" t="n">
-        <v>4.6</v>
+        <v>8.5</v>
       </c>
       <c r="N35" t="n">
-        <v>6.25</v>
+        <v>18</v>
       </c>
       <c r="O35" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R35" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="T35" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="U35" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X35" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>3.27</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['10', '66', '90+2']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.81</v>
+        <v>5.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45622.70833333334</v>
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="M36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O36" t="n">
         <v>6</v>
       </c>
-      <c r="N36" t="n">
-        <v>11</v>
-      </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U36" t="n">
         <v>1.57</v>
       </c>
-      <c r="P36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>9</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.8</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['8', '11', '30', '61', '72']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '28', '31', '39', '56', '90']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.02</v>
+        <v>2.99</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.65</v>
+        <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.18</v>
+        <v>3.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45622.70833333334</v>
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,65 +5184,65 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="M37" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="T37" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="U37" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['8', '11', '30', '61', '72']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.3</v>
+        <v>4.65</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45622.70833333334</v>
@@ -5287,109 +5287,109 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X38" t="n">
         <v>4</v>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="Y38" t="n">
         <v>1.66</v>
       </c>
-      <c r="O38" t="n">
-        <v>6</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X38" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.61</v>
-      </c>
       <c r="Z38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD38" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2</v>
-      </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['9', '28', '31', '39', '56', '90']</t>
+          <t>['7', '22', '45+1', '65', '82']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>2.99</v>
+        <v>1.65</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45622.70833333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,109 +5416,109 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O39" t="n">
         <v>3</v>
       </c>
-      <c r="H39" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M39" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="N39" t="n">
-        <v>15</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.57</v>
-      </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="S39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA39" t="n">
         <v>4.33</v>
       </c>
-      <c r="T39" t="n">
-        <v>2</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="AB39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1.73</v>
       </c>
-      <c r="V39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X39" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['44', '50', '53']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['74', '82', '89']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AJ39" t="n">
-        <v>4.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45622.70833333334</v>
@@ -5545,19 +5545,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -5571,22 +5571,22 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="M40" t="n">
-        <v>8.5</v>
+        <v>7.75</v>
       </c>
       <c r="N40" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O40" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P40" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="R40" t="n">
         <v>1.2</v>
@@ -5595,59 +5595,59 @@
         <v>4.33</v>
       </c>
       <c r="T40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X40" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.27</v>
+        <v>2.99</v>
       </c>
       <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB40" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['10', '66', '90+2']</t>
+          <t>['44', '50', '53']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74', '82', '89']</t>
         </is>
       </c>
       <c r="AG40" t="n">
         <v>1.01</v>
       </c>
       <c r="AH40" t="n">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AI40" t="n">
         <v>1.17</v>
       </c>
       <c r="AJ40" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45622.70833333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH41" t="n">
         <v>2.3</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>3</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AI41" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45622.70833333334</v>
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.25</v>
+        <v>1.49</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N42" t="n">
-        <v>2.1</v>
+        <v>6.25</v>
       </c>
       <c r="O42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S42" t="n">
         <v>3.5</v>
       </c>
-      <c r="P42" t="n">
+      <c r="T42" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U42" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="X42" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA42" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['7', '22', '45+1', '65', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>2.81</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.73</v>
+        <v>3.4</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45622.70833333334</v>
@@ -6835,25 +6835,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M50" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N50" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="O50" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="P50" t="n">
         <v>1.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R50" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="S50" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="T50" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="U50" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V50" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="W50" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="X50" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="Y50" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AA50" t="n">
-        <v>5.31</v>
+        <v>7.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['5', '90']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['30', '45+3', '61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45622.88541666666</v>
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M51" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N51" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="O51" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="P51" t="n">
         <v>1.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="T51" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="U51" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V51" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.14</v>
       </c>
-      <c r="W51" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC51" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['5', '90']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '45+3', '61']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45622.88541666666</v>
@@ -7093,16 +7093,16 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
         <v>3</v>
@@ -7119,31 +7119,31 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="M52" t="n">
         <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O52" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="P52" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S52" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U52" t="n">
         <v>1.36</v>
@@ -7152,50 +7152,50 @@
         <v>1.05</v>
       </c>
       <c r="W52" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X52" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y52" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC52" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD52" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['73', '81']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['19', '73', '89']</t>
+          <t>['22', '67', '90+3']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH52" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45622.89583333334</v>
@@ -7222,16 +7222,16 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>3</v>
@@ -7248,31 +7248,31 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M53" t="n">
         <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="P53" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="R53" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T53" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U53" t="n">
         <v>1.36</v>
@@ -7281,50 +7281,50 @@
         <v>1.05</v>
       </c>
       <c r="W53" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X53" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Y53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC53" t="n">
         <v>1.91</v>
       </c>
-      <c r="Z53" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD53" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['73', '81']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['22', '67', '90+3']</t>
+          <t>['19', '73', '89']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45622.89583333334</v>
